--- a/validation/Excel Data Analyzer - Validation Data.xlsx
+++ b/validation/Excel Data Analyzer - Validation Data.xlsx
@@ -437,7 +437,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">  • Payments September — the main validation sheet, 31 records.</v>
+        <v xml:space="preserve">  • Payments September — the main validation sheet, 33 records.</v>
       </c>
     </row>
     <row r="11">
@@ -464,7 +464,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G34"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -1211,9 +1211,55 @@
         <v>Date written as text: 25/09/2026</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="1">
+        <v>46291.604166666664</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Naveen Rao</v>
+      </c>
+      <c r="C33" t="str">
+        <v>UP32DT1001</v>
+      </c>
+      <c r="D33" t="str">
+        <v>UPI</v>
+      </c>
+      <c r="E33">
+        <v>1250</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Fuel</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Date cell with a time of day (26/09/2026 14:30)</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Tanvi Desai</v>
+      </c>
+      <c r="C34" t="str">
+        <v>UP65IJ8901</v>
+      </c>
+      <c r="D34" t="str">
+        <v>UPI</v>
+      </c>
+      <c r="E34">
+        <v>3000</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Fuel</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Near duplicate comparison row — remark changed</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G34"/>
   </ignoredErrors>
 </worksheet>
 </file>
